--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479022</v>
+        <v>123479017</v>
       </c>
       <c r="B2" t="n">
         <v>56373</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483365</v>
+        <v>483373</v>
       </c>
       <c r="R2" t="n">
-        <v>7008077</v>
+        <v>7008072</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479016</v>
+        <v>123479021</v>
       </c>
       <c r="B3" t="n">
         <v>56373</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483373</v>
+        <v>483365</v>
       </c>
       <c r="R3" t="n">
-        <v>7008072</v>
+        <v>7008077</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479021</v>
+        <v>123479019</v>
       </c>
       <c r="B2" t="n">
-        <v>56373</v>
+        <v>56379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123479017</v>
       </c>
       <c r="B3" t="n">
-        <v>56373</v>
+        <v>56379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479019</v>
+        <v>123479017</v>
       </c>
       <c r="B2" t="n">
-        <v>56379</v>
+        <v>56382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483365</v>
+        <v>483373</v>
       </c>
       <c r="R2" t="n">
-        <v>7008077</v>
+        <v>7008072</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479017</v>
+        <v>123479019</v>
       </c>
       <c r="B3" t="n">
-        <v>56379</v>
+        <v>56382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483373</v>
+        <v>483365</v>
       </c>
       <c r="R3" t="n">
-        <v>7008072</v>
+        <v>7008077</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479017</v>
+        <v>123479016</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479019</v>
+        <v>123479026</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479016</v>
+        <v>123479014</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479026</v>
+        <v>123479025</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479014</v>
+        <v>123479026</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483373</v>
+        <v>483365</v>
       </c>
       <c r="R2" t="n">
-        <v>7008072</v>
+        <v>7008077</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,14 +794,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479025</v>
+        <v>123479014</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483365</v>
+        <v>483373</v>
       </c>
       <c r="R3" t="n">
-        <v>7008077</v>
+        <v>7008072</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479026</v>
+        <v>123479022</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,14 +794,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479014</v>
+        <v>123479017</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479022</v>
+        <v>123479021</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479017</v>
+        <v>123479014</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29058-2019 artfynd.xlsx
+++ b/artfynd/A 29058-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123479021</v>
+        <v>123479026</v>
       </c>
       <c r="B2" t="n">
         <v>56382</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123479014</v>
+        <v>123479017</v>
       </c>
       <c r="B3" t="n">
         <v>56382</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
